--- a/data/WP17_auswertung_ministerien.xlsx
+++ b/data/WP17_auswertung_ministerien.xlsx
@@ -1054,13 +1054,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F19DD53C-8487-4B96-8F68-467A29EC2479}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{973135B9-ACD9-421B-873A-804A6454BC9A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73569090-8FFD-4B9C-A363-1FDF22683C0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13699B4B-FBFD-4013-8AE1-111D6D825C88}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C84B231-2BDC-4C70-8C40-09EB1FAD07F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37903BD1-8B5D-4DE3-A67A-A390B3CA6878}"/>
 </file>